--- a/InputData/indst/CNBEIR/Cement New Build Energy Intensity Ratio.xlsx
+++ b/InputData/indst/CNBEIR/Cement New Build Energy Intensity Ratio.xlsx
@@ -746,11 +746,11 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Precalciner CNBEIR (unrounded) = BAT / fleet-typical</t>
+          <t>Precalciner CNBEIR (unrounded) = BAT (GJ/t, converted to MMBtu at 1.05506 GJ per MMBtu) / fleet-typical (MMBtu/t)</t>
         </is>
       </c>
       <c r="B8">
-        <f>B4/B7</f>
+        <f>B4/1.05506/B7</f>
         <v/>
       </c>
     </row>
@@ -768,7 +768,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>Dry kiln with CCS</t>
+          <t>Dry kiln with CCS: equals the dry kiln since 2026-10-01 (CEIbPaF CCS row is kiln-only; capture energy is booked by the CCS sector)</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="B17">
-        <f>(B15*B12+B16*B14)/B13</f>
+        <f>B9</f>
         <v/>
       </c>
     </row>
@@ -883,7 +883,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Held flat 2021-2050 for all four pathways (see About Notes)</t>
+          <t>Held flat 2021-2050 for all four pathways (see About Notes). Unit fix 2026-10-01: the earlier 0.846 divided GJ by MMBtu without converting.</t>
         </is>
       </c>
     </row>
@@ -908,6 +908,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
@@ -1012,94 +1013,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="C4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="D4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="E4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="F4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="G4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="H4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="I4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="J4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="K4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="L4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="M4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="N4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="O4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="P4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="R4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="S4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="T4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="U4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="V4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="W4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="X4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="5">
@@ -1356,6 +1357,7 @@
         <v/>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
@@ -1363,94 +1365,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="C8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="D8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="E8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="F8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="G8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="H8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="I8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="J8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="K8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="L8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="M8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="N8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="O8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="P8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="R8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="S8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="T8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="U8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="V8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="W8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="X8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="9">
@@ -1707,6 +1709,7 @@
         <v/>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -2058,6 +2061,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -2409,6 +2413,8 @@
         <v/>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
@@ -2553,7 +2559,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Unit: dimensionless (DRAFT by pathway: precalciner 0.846 = 2.9/3.43 GJ/t DOE Bandwidth; CCS 0.901 kiln-component-only BAT; electric/alt-chem 1.0 already-BAT - verify before release)</t>
+          <t>Unit: dimensionless (DRAFT by pathway: precalciner 0.802 = 2.9 GJ/t BAT over 3.43 MMBtu/t fleet-typical, DOE Bandwidth, GJ-to-MMBtu corrected 2026-10-01; CCS = dry kiln value (CEIbPaF CCS row is kiln-only since 2026-10-01; capture energy sits in the CCS sector); electric/alt-chem 1.0 already-BAT - verify before release)</t>
         </is>
       </c>
       <c r="B1" t="n">
@@ -2654,94 +2660,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="C2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="D2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="E2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="F2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="G2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="H2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="I2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="K2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="L2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="M2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="N2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="O2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="P2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="R2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="S2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="T2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="U2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="V2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="W2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="X2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.846</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="3">
@@ -2751,94 +2757,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="C3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="D3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="E3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="F3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="G3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="H3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="I3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="J3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="K3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="L3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="M3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="N3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="O3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="P3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="R3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="S3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="T3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="U3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="V3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="W3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="X3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.901</v>
+        <v>0.802</v>
       </c>
     </row>
     <row r="4">
